--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-09_ekipman_kabul_raporu_ve_ekipman_teknik_dosyasi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-FRM-09_ekipman_kabul_raporu_ve_ekipman_teknik_dosyasi.xlsx
@@ -1018,7 +1018,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Ekipman Kabul Raporu ve Ekipman Teknik Dosyası</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Yeterli ekipman kabul içeriği korundu; tekrar deneme kimliği ve sınırlı kullanım kararının sınırları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc7e224c74d4228"/>
   <x:tableParts count="1">
@@ -1444,7 +1445,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Ekipman Kabul Raporu ve Ekipman Teknik Dosyası</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Yeterli ekipman kabul içeriği korundu; tekrar deneme kimliği ve sınırlı kullanım kararının sınırları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45f6bef3a66748d7"/>
   <x:tableParts count="1">
@@ -1824,7 +1826,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Ekipman Kabul Raporu ve Ekipman Teknik Dosyası</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Yeterli ekipman kabul içeriği korundu; tekrar deneme kimliği ve sınırlı kullanım kararının sınırları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5c301fd158f4e40"/>
   <x:tableParts count="1">
@@ -2141,7 +2144,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-09&amp;C&amp;"Arial,Regular"&amp;11Ekipman Kabul Raporu ve Ekipman Teknik Dosyası</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Yeterli ekipman kabul içeriği korundu; tekrar deneme kimliği ve sınırlı kullanım kararının sınırları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e214c8adfb14349"/>
   <x:tableParts count="1">
